--- a/sheets/S08A22P210.xlsx
+++ b/sheets/S08A22P210.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5224" uniqueCount="1317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5464" uniqueCount="1327">
   <si>
     <t>Voter ID</t>
   </si>
@@ -3962,6 +3962,36 @@
   </si>
   <si>
     <t>Kastoori</t>
+  </si>
+  <si>
+    <t>Amanpreet Kaur</t>
+  </si>
+  <si>
+    <t>Navin Kumar</t>
+  </si>
+  <si>
+    <t>Dharm Bir</t>
+  </si>
+  <si>
+    <t>Jagveer Singh</t>
+  </si>
+  <si>
+    <t>Tikaram</t>
+  </si>
+  <si>
+    <t>Pavankumar</t>
+  </si>
+  <si>
+    <t>Tejveer</t>
+  </si>
+  <si>
+    <t>Jagvir Singh</t>
+  </si>
+  <si>
+    <t>Shila Devi</t>
+  </si>
+  <si>
+    <t>Indrajit</t>
   </si>
 </sst>
 </file>
@@ -4342,7 +4372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H653"/>
+  <dimension ref="A1:H683"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -21330,6 +21360,786 @@
         <v>15</v>
       </c>
     </row>
+    <row r="654" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A654" t="s">
+        <v>8</v>
+      </c>
+      <c r="B654" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C654" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D654" t="s">
+        <v>11</v>
+      </c>
+      <c r="E654" t="s">
+        <v>12</v>
+      </c>
+      <c r="F654" t="s">
+        <v>13</v>
+      </c>
+      <c r="G654" t="s">
+        <v>14</v>
+      </c>
+      <c r="H654" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="655" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A655" t="s">
+        <v>16</v>
+      </c>
+      <c r="B655" t="s">
+        <v>17</v>
+      </c>
+      <c r="C655" t="s">
+        <v>18</v>
+      </c>
+      <c r="D655" t="s">
+        <v>11</v>
+      </c>
+      <c r="E655" t="s">
+        <v>12</v>
+      </c>
+      <c r="F655" t="s">
+        <v>13</v>
+      </c>
+      <c r="G655" t="s">
+        <v>14</v>
+      </c>
+      <c r="H655" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="656" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A656" t="s">
+        <v>19</v>
+      </c>
+      <c r="B656" t="s">
+        <v>20</v>
+      </c>
+      <c r="C656" t="s">
+        <v>21</v>
+      </c>
+      <c r="D656" t="s">
+        <v>11</v>
+      </c>
+      <c r="E656" t="s">
+        <v>12</v>
+      </c>
+      <c r="F656" t="s">
+        <v>13</v>
+      </c>
+      <c r="G656" t="s">
+        <v>14</v>
+      </c>
+      <c r="H656" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="657" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A657" t="s">
+        <v>22</v>
+      </c>
+      <c r="B657" t="s">
+        <v>23</v>
+      </c>
+      <c r="C657" t="s">
+        <v>24</v>
+      </c>
+      <c r="D657" t="s">
+        <v>11</v>
+      </c>
+      <c r="E657" t="s">
+        <v>12</v>
+      </c>
+      <c r="F657" t="s">
+        <v>13</v>
+      </c>
+      <c r="G657" t="s">
+        <v>14</v>
+      </c>
+      <c r="H657" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="658" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A658" t="s">
+        <v>25</v>
+      </c>
+      <c r="B658" t="s">
+        <v>26</v>
+      </c>
+      <c r="C658" t="s">
+        <v>27</v>
+      </c>
+      <c r="D658" t="s">
+        <v>11</v>
+      </c>
+      <c r="E658" t="s">
+        <v>12</v>
+      </c>
+      <c r="F658" t="s">
+        <v>13</v>
+      </c>
+      <c r="G658" t="s">
+        <v>14</v>
+      </c>
+      <c r="H658" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="659" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A659" t="s">
+        <v>28</v>
+      </c>
+      <c r="B659" t="s">
+        <v>29</v>
+      </c>
+      <c r="C659" t="s">
+        <v>27</v>
+      </c>
+      <c r="D659" t="s">
+        <v>11</v>
+      </c>
+      <c r="E659" t="s">
+        <v>12</v>
+      </c>
+      <c r="F659" t="s">
+        <v>13</v>
+      </c>
+      <c r="G659" t="s">
+        <v>14</v>
+      </c>
+      <c r="H659" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="660" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A660" t="s">
+        <v>30</v>
+      </c>
+      <c r="B660" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C660" t="s">
+        <v>24</v>
+      </c>
+      <c r="D660" t="s">
+        <v>11</v>
+      </c>
+      <c r="E660" t="s">
+        <v>12</v>
+      </c>
+      <c r="F660" t="s">
+        <v>13</v>
+      </c>
+      <c r="G660" t="s">
+        <v>14</v>
+      </c>
+      <c r="H660" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="661" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A661" t="s">
+        <v>32</v>
+      </c>
+      <c r="B661" t="s">
+        <v>33</v>
+      </c>
+      <c r="C661" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D661" t="s">
+        <v>11</v>
+      </c>
+      <c r="E661" t="s">
+        <v>12</v>
+      </c>
+      <c r="F661" t="s">
+        <v>13</v>
+      </c>
+      <c r="G661" t="s">
+        <v>14</v>
+      </c>
+      <c r="H661" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="662" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A662" t="s">
+        <v>34</v>
+      </c>
+      <c r="B662" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C662" t="s">
+        <v>24</v>
+      </c>
+      <c r="D662" t="s">
+        <v>11</v>
+      </c>
+      <c r="E662" t="s">
+        <v>12</v>
+      </c>
+      <c r="F662" t="s">
+        <v>13</v>
+      </c>
+      <c r="G662" t="s">
+        <v>14</v>
+      </c>
+      <c r="H662" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="663" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A663" t="s">
+        <v>36</v>
+      </c>
+      <c r="B663" t="s">
+        <v>37</v>
+      </c>
+      <c r="C663" t="s">
+        <v>38</v>
+      </c>
+      <c r="D663" t="s">
+        <v>11</v>
+      </c>
+      <c r="E663" t="s">
+        <v>12</v>
+      </c>
+      <c r="F663" t="s">
+        <v>13</v>
+      </c>
+      <c r="G663" t="s">
+        <v>14</v>
+      </c>
+      <c r="H663" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="664" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A664" t="s">
+        <v>39</v>
+      </c>
+      <c r="B664" t="s">
+        <v>652</v>
+      </c>
+      <c r="C664" t="s">
+        <v>713</v>
+      </c>
+      <c r="D664" t="s">
+        <v>11</v>
+      </c>
+      <c r="E664" t="s">
+        <v>12</v>
+      </c>
+      <c r="F664" t="s">
+        <v>13</v>
+      </c>
+      <c r="G664" t="s">
+        <v>14</v>
+      </c>
+      <c r="H664" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="665" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A665" t="s">
+        <v>42</v>
+      </c>
+      <c r="B665" t="s">
+        <v>43</v>
+      </c>
+      <c r="C665" t="s">
+        <v>44</v>
+      </c>
+      <c r="D665" t="s">
+        <v>11</v>
+      </c>
+      <c r="E665" t="s">
+        <v>12</v>
+      </c>
+      <c r="F665" t="s">
+        <v>13</v>
+      </c>
+      <c r="G665" t="s">
+        <v>14</v>
+      </c>
+      <c r="H665" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="666" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A666" t="s">
+        <v>45</v>
+      </c>
+      <c r="B666" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C666" t="s">
+        <v>47</v>
+      </c>
+      <c r="D666" t="s">
+        <v>11</v>
+      </c>
+      <c r="E666" t="s">
+        <v>12</v>
+      </c>
+      <c r="F666" t="s">
+        <v>13</v>
+      </c>
+      <c r="G666" t="s">
+        <v>14</v>
+      </c>
+      <c r="H666" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="667" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A667" t="s">
+        <v>48</v>
+      </c>
+      <c r="B667" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C667" t="s">
+        <v>50</v>
+      </c>
+      <c r="D667" t="s">
+        <v>11</v>
+      </c>
+      <c r="E667" t="s">
+        <v>12</v>
+      </c>
+      <c r="F667" t="s">
+        <v>13</v>
+      </c>
+      <c r="G667" t="s">
+        <v>14</v>
+      </c>
+      <c r="H667" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="668" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A668" t="s">
+        <v>51</v>
+      </c>
+      <c r="B668" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C668" t="s">
+        <v>24</v>
+      </c>
+      <c r="D668" t="s">
+        <v>11</v>
+      </c>
+      <c r="E668" t="s">
+        <v>12</v>
+      </c>
+      <c r="F668" t="s">
+        <v>13</v>
+      </c>
+      <c r="G668" t="s">
+        <v>14</v>
+      </c>
+      <c r="H668" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="669" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A669" t="s">
+        <v>53</v>
+      </c>
+      <c r="B669" t="s">
+        <v>54</v>
+      </c>
+      <c r="C669" t="s">
+        <v>55</v>
+      </c>
+      <c r="D669" t="s">
+        <v>11</v>
+      </c>
+      <c r="E669" t="s">
+        <v>12</v>
+      </c>
+      <c r="F669" t="s">
+        <v>13</v>
+      </c>
+      <c r="G669" t="s">
+        <v>14</v>
+      </c>
+      <c r="H669" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="670" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A670" t="s">
+        <v>56</v>
+      </c>
+      <c r="B670" t="s">
+        <v>57</v>
+      </c>
+      <c r="C670" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D670" t="s">
+        <v>11</v>
+      </c>
+      <c r="E670" t="s">
+        <v>12</v>
+      </c>
+      <c r="F670" t="s">
+        <v>13</v>
+      </c>
+      <c r="G670" t="s">
+        <v>14</v>
+      </c>
+      <c r="H670" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="671" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A671" t="s">
+        <v>58</v>
+      </c>
+      <c r="B671" t="s">
+        <v>59</v>
+      </c>
+      <c r="C671" t="s">
+        <v>60</v>
+      </c>
+      <c r="D671" t="s">
+        <v>11</v>
+      </c>
+      <c r="E671" t="s">
+        <v>12</v>
+      </c>
+      <c r="F671" t="s">
+        <v>13</v>
+      </c>
+      <c r="G671" t="s">
+        <v>14</v>
+      </c>
+      <c r="H671" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="672" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A672" t="s">
+        <v>61</v>
+      </c>
+      <c r="B672" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C672" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D672" t="s">
+        <v>11</v>
+      </c>
+      <c r="E672" t="s">
+        <v>12</v>
+      </c>
+      <c r="F672" t="s">
+        <v>13</v>
+      </c>
+      <c r="G672" t="s">
+        <v>14</v>
+      </c>
+      <c r="H672" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="673" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A673" t="s">
+        <v>63</v>
+      </c>
+      <c r="B673" t="s">
+        <v>64</v>
+      </c>
+      <c r="C673" t="s">
+        <v>65</v>
+      </c>
+      <c r="D673" t="s">
+        <v>11</v>
+      </c>
+      <c r="E673" t="s">
+        <v>12</v>
+      </c>
+      <c r="F673" t="s">
+        <v>13</v>
+      </c>
+      <c r="G673" t="s">
+        <v>14</v>
+      </c>
+      <c r="H673" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="674" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A674" t="s">
+        <v>66</v>
+      </c>
+      <c r="B674" t="s">
+        <v>67</v>
+      </c>
+      <c r="C674" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D674" t="s">
+        <v>11</v>
+      </c>
+      <c r="E674" t="s">
+        <v>12</v>
+      </c>
+      <c r="F674" t="s">
+        <v>13</v>
+      </c>
+      <c r="G674" t="s">
+        <v>14</v>
+      </c>
+      <c r="H674" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="675" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A675" t="s">
+        <v>69</v>
+      </c>
+      <c r="B675" t="s">
+        <v>70</v>
+      </c>
+      <c r="C675" t="s">
+        <v>71</v>
+      </c>
+      <c r="D675" t="s">
+        <v>11</v>
+      </c>
+      <c r="E675" t="s">
+        <v>12</v>
+      </c>
+      <c r="F675" t="s">
+        <v>13</v>
+      </c>
+      <c r="G675" t="s">
+        <v>14</v>
+      </c>
+      <c r="H675" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="676" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A676" t="s">
+        <v>72</v>
+      </c>
+      <c r="B676" t="s">
+        <v>73</v>
+      </c>
+      <c r="C676" t="s">
+        <v>74</v>
+      </c>
+      <c r="D676" t="s">
+        <v>11</v>
+      </c>
+      <c r="E676" t="s">
+        <v>12</v>
+      </c>
+      <c r="F676" t="s">
+        <v>13</v>
+      </c>
+      <c r="G676" t="s">
+        <v>14</v>
+      </c>
+      <c r="H676" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="677" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A677" t="s">
+        <v>75</v>
+      </c>
+      <c r="B677" t="s">
+        <v>76</v>
+      </c>
+      <c r="C677" t="s">
+        <v>73</v>
+      </c>
+      <c r="D677" t="s">
+        <v>11</v>
+      </c>
+      <c r="E677" t="s">
+        <v>12</v>
+      </c>
+      <c r="F677" t="s">
+        <v>13</v>
+      </c>
+      <c r="G677" t="s">
+        <v>14</v>
+      </c>
+      <c r="H677" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="678" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A678" t="s">
+        <v>77</v>
+      </c>
+      <c r="B678" t="s">
+        <v>78</v>
+      </c>
+      <c r="C678" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D678" t="s">
+        <v>11</v>
+      </c>
+      <c r="E678" t="s">
+        <v>12</v>
+      </c>
+      <c r="F678" t="s">
+        <v>13</v>
+      </c>
+      <c r="G678" t="s">
+        <v>14</v>
+      </c>
+      <c r="H678" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="679" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A679" t="s">
+        <v>80</v>
+      </c>
+      <c r="B679" t="s">
+        <v>81</v>
+      </c>
+      <c r="C679" t="s">
+        <v>74</v>
+      </c>
+      <c r="D679" t="s">
+        <v>11</v>
+      </c>
+      <c r="E679" t="s">
+        <v>12</v>
+      </c>
+      <c r="F679" t="s">
+        <v>13</v>
+      </c>
+      <c r="G679" t="s">
+        <v>14</v>
+      </c>
+      <c r="H679" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="680" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A680" t="s">
+        <v>82</v>
+      </c>
+      <c r="B680" t="s">
+        <v>83</v>
+      </c>
+      <c r="C680" t="s">
+        <v>46</v>
+      </c>
+      <c r="D680" t="s">
+        <v>11</v>
+      </c>
+      <c r="E680" t="s">
+        <v>12</v>
+      </c>
+      <c r="F680" t="s">
+        <v>13</v>
+      </c>
+      <c r="G680" t="s">
+        <v>14</v>
+      </c>
+      <c r="H680" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="681" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A681" t="s">
+        <v>84</v>
+      </c>
+      <c r="B681" t="s">
+        <v>17</v>
+      </c>
+      <c r="C681" t="s">
+        <v>85</v>
+      </c>
+      <c r="D681" t="s">
+        <v>11</v>
+      </c>
+      <c r="E681" t="s">
+        <v>12</v>
+      </c>
+      <c r="F681" t="s">
+        <v>13</v>
+      </c>
+      <c r="G681" t="s">
+        <v>14</v>
+      </c>
+      <c r="H681" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="682" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A682" t="s">
+        <v>86</v>
+      </c>
+      <c r="B682" t="s">
+        <v>87</v>
+      </c>
+      <c r="C682" t="s">
+        <v>652</v>
+      </c>
+      <c r="D682" t="s">
+        <v>11</v>
+      </c>
+      <c r="E682" t="s">
+        <v>12</v>
+      </c>
+      <c r="F682" t="s">
+        <v>13</v>
+      </c>
+      <c r="G682" t="s">
+        <v>14</v>
+      </c>
+      <c r="H682" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="683" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A683" t="s">
+        <v>88</v>
+      </c>
+      <c r="B683" t="s">
+        <v>89</v>
+      </c>
+      <c r="C683" t="s">
+        <v>74</v>
+      </c>
+      <c r="D683" t="s">
+        <v>11</v>
+      </c>
+      <c r="E683" t="s">
+        <v>12</v>
+      </c>
+      <c r="F683" t="s">
+        <v>13</v>
+      </c>
+      <c r="G683" t="s">
+        <v>14</v>
+      </c>
+      <c r="H683" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
